--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260921.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260921.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14129,7 +14129,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14397,7 +14397,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17479,7 +17479,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18216,7 +18216,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18350,7 +18350,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18953,7 +18953,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20360,7 +20360,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21097,7 +21097,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21164,7 +21164,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21231,7 +21231,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21432,7 +21432,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21901,7 +21901,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22102,7 +22102,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22169,7 +22169,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22303,7 +22303,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22370,7 +22370,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22437,7 +22437,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S328" t="inlineStr"/>
@@ -22586,7 +22586,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S329" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="S330" t="inlineStr"/>

--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260921.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260921.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14129,7 +14129,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14397,7 +14397,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17479,7 +17479,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18216,7 +18216,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18350,7 +18350,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18953,7 +18953,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20360,7 +20360,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21097,7 +21097,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21164,7 +21164,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21231,7 +21231,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21432,7 +21432,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21901,7 +21901,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22102,7 +22102,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22169,7 +22169,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22303,7 +22303,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22370,7 +22370,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22437,7 +22437,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S328" t="inlineStr"/>
@@ -22586,7 +22586,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S329" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:11</t>
+          <t>2026-09-21 15:17:31</t>
         </is>
       </c>
       <c r="S330" t="inlineStr"/>
